--- a/artfynd/A 3945-2022 artfynd.xlsx
+++ b/artfynd/A 3945-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3945-2022 artfynd.xlsx
+++ b/artfynd/A 3945-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104230881</v>
+        <v>95492734</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogarna runt Norra Bocksjön, Nrk</t>
+          <t>Sandbacken Ö, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488917.5495242738</v>
+        <v>488952</v>
       </c>
       <c r="R2" t="n">
-        <v>6521000.983729089</v>
+        <v>6521094</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-03-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Måttligt mycket, frisk</t>
+          <t>2021-03-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,27 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>David Tverling, Lovisa Larsson, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Miniforskningsresan Extensus Örebro län 2021</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>113912242</v>
       </c>
       <c r="B3" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,15 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113912218</v>
+        <v>95492733</v>
       </c>
       <c r="B4" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,27 +915,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stora Björstorp, Nrk</t>
+          <t>Sandbacken Ö, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488925</v>
+        <v>488950</v>
       </c>
       <c r="R4" t="n">
-        <v>6521038</v>
+        <v>6521137</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,17 +951,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2021-03-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2021-03-16</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Vinterspillning, spridd under äldre tall.</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,15 +976,541 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>David Tverling, Lovisa Larsson, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Miniforskningsresan Extensus Örebro län 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>95492735</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sandbacken Ö, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>488991</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6521077</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-03-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-03-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>David Tverling, Lovisa Larsson, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Miniforskningsresan Extensus Örebro län 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>113912218</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stora Björstorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>488925</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6521038</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Vinterspillning, spridd under äldre tall.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Lars Gerre</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Lars Gerre</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118352316</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>NO om Sandbacken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>488932</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6521127</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Lyfte från tall.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>104230881</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skogarna runt Norra Bocksjön, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>488917</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6521001</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-10-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-10-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Måttligt mycket, frisk</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>104231000</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skogarna runt Norra Bocksjön, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>489054</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6521088</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Fertil, mindre bestånd</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3945-2022 artfynd.xlsx
+++ b/artfynd/A 3945-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Miniforskningsresan Extensus Örebro län 2021</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95492734</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113912242</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
           <t>Miniforskningsresan Extensus Örebro län 2021</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95492733</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
           <t>Miniforskningsresan Extensus Örebro län 2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95492735</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113912218</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1307,6 +1337,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118352316</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1409,6 +1444,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104230881</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1511,8 +1551,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104231000</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>